--- a/tame_output/ON/bt/strategyON_20231121.xlsx
+++ b/tame_output/ON/bt/strategyON_20231121.xlsx
@@ -595,7 +595,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>51.2%</t>
+          <t>51.4%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -605,7 +605,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -614,7 +614,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1784</v>
+        <v>1785</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2023-11-19</t>
+          <t>2023-11-20</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -736,7 +736,7 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>90.5%</t>
+          <t>91.3%</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>80.7%</t>
+          <t>80.3%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -758,7 +758,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.79</t>
+          <t>2.78</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -767,7 +767,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1784</v>
+        <v>1785</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -776,7 +776,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2023-11-19</t>
+          <t>2023-11-20</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -839,7 +839,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>67.2%</t>
+          <t>66.9%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -864,7 +864,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.9%</t>
+          <t>39.8%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -889,7 +889,7 @@
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>24.6%</t>
+          <t>23.8%</t>
         </is>
       </c>
     </row>
@@ -906,7 +906,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>32.8%</t>
+          <t>32.7%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -916,11 +916,11 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.9%</t>
+          <t>52.8%</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1784</v>
+        <v>1785</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2023-11-19</t>
+          <t>2023-11-20</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>52.8%</t>
+          <t>52.9%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1054,7 +1054,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>103.9%</t>
+          <t>103.5%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1064,16 +1064,16 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>3.30</t>
+          <t>3.29</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>58.6%</t>
+          <t>58.5%</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1784</v>
+        <v>1785</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2023-11-19</t>
+          <t>2023-11-20</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1130,7 +1130,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>8.6%</t>
+          <t>8.5%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>99.2%</t>
+          <t>98.8%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1170,7 +1170,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>40.6%</t>
+          <t>40.5%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>30.5%</t>
+          <t>29.8%</t>
         </is>
       </c>
     </row>
@@ -1226,7 +1226,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1784</v>
+        <v>1785</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1235,7 +1235,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2023-11-19</t>
+          <t>2023-11-20</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>9.4%</t>
+          <t>9.5%</t>
         </is>
       </c>
     </row>
@@ -1360,7 +1360,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>133.9%</t>
+          <t>133.4%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1370,16 +1370,16 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>4.16</t>
+          <t>4.15</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.9%</t>
+          <t>59.8%</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1784</v>
+        <v>1785</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2023-11-19</t>
+          <t>2023-11-20</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1436,7 +1436,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>9.3%</t>
+          <t>9.2%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>127.8%</t>
+          <t>127.3%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>30.3%</t>
+          <t>29.6%</t>
         </is>
       </c>
     </row>
@@ -1516,7 +1516,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1787"/>
+  <dimension ref="A1:G1788"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -42611,7 +42611,7 @@
         <v>45249</v>
       </c>
       <c r="B1787" t="n">
-        <v>3.140086936175495</v>
+        <v>3.141819250502547</v>
       </c>
       <c r="C1787" t="n">
         <v>3.100925124196311</v>
@@ -42627,6 +42627,29 @@
       </c>
       <c r="G1787" t="n">
         <v>4.413196291434393</v>
+      </c>
+    </row>
+    <row r="1788">
+      <c r="A1788" s="2" t="n">
+        <v>45250</v>
+      </c>
+      <c r="B1788" t="n">
+        <v>3.148611740249846</v>
+      </c>
+      <c r="C1788" t="n">
+        <v>3.09333980438922</v>
+      </c>
+      <c r="D1788" t="n">
+        <v>1.572667960338027</v>
+      </c>
+      <c r="E1788" t="n">
+        <v>3.722050564210684</v>
+      </c>
+      <c r="F1788" t="n">
+        <v>2.187881872752795</v>
+      </c>
+      <c r="G1788" t="n">
+        <v>4.406068928040899</v>
       </c>
     </row>
   </sheetData>
